--- a/规划/C++就业方向（程序员段亮亮）.xlsx
+++ b/规划/C++就业方向（程序员段亮亮）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="C++1" sheetId="5" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="154">
   <si>
     <t>C++就业方向</t>
   </si>
@@ -108,34 +108,16 @@
 各种地方性自动化公司：产线监控系统、上位机、工厂数字化改造</t>
   </si>
   <si>
-    <t>嵌入式设备/消费电子 / IoT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 中偏多</t>
-  </si>
-  <si>
-    <t>低偏中
-（双非本）</t>
-  </si>
-  <si>
-    <t>嵌入式软件/ Linux软件 / MCU软件 / 单片机 / 物联网终端 / IoT网关 / 机顶盒软件 / 多媒体终端软件开发工程师</t>
+    <t>医疗设备/医疗影像&amp;监护</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>医疗设备软件 / 医学影像软件 / DICOM软件 / PACS软件 / 医疗监护系统 /医疗设备嵌入式/ 医疗信息系统客户端开发工程师</t>
   </si>
   <si>
     <t>等我出视频</t>
-  </si>
-  <si>
-    <t>IoT 平台：涂鸦、机智云、阿里云 IoT、华为 HiLink 等
-智能硬件：小米生态链、绿米、各类做路由器、摄像头、穿戴公司
-家电：美的、格力、海尔等的智能家电控制板软件团队</t>
-  </si>
-  <si>
-    <t>医疗设备/医疗影像&amp;监护</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>医疗设备软件 / 医学影像软件 / DICOM软件 / PACS软件 / 医疗监护系统 /医疗设备嵌入式/ 医疗信息系统客户端开发工程师</t>
   </si>
   <si>
     <t>影像类：联影、迈瑞、东软医疗、万东、开立等
@@ -157,6 +139,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF800080"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="0"/>
+      </rPr>
       <t>https://www.bilibili.com/video/BV1WJSvBcEQz
 本质还是linux后台技术栈（</t>
     </r>
@@ -218,6 +207,9 @@
     <t>汽车&amp;智能驾驶/车路协同</t>
   </si>
   <si>
+    <t xml:space="preserve"> 中偏多</t>
+  </si>
+  <si>
     <t>车载软件/自动驾驶/自动驾驶仿真平台/智能座舱系统/车路协同通信工程师</t>
   </si>
   <si>
@@ -228,45 +220,6 @@
     <t>主机厂：比亚迪、蔚来、小鹏、理想、上汽、广汽、长安、吉利
 智驾方案商：地平线、毫末、Momenta、智加、蘑菇车联、华为 ADS等
 车路协同：华为、四维图新、千方科技等的智能交通 &amp; V2X 方案</t>
-  </si>
-  <si>
-    <t>机器人 / 智能制造 / 移动机器人（C++）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中偏高
-</t>
-  </si>
-  <si>
-    <t>工业机器人控制 / 机器人运动控制算法 / 移动机器人导航与路径规划 / 机器人上位机 / 机器人中间件/ 机器人仿真</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.bilibili.com/video/BV1ApqfBAE9n
-</t>
-  </si>
-  <si>
-    <t>工业机器人：汇川、埃斯顿、新松、节卡 JAKA、遨博、ABB、KUKA、FANUC、安川等
-移动机器人：海柔创新、极智嘉 Geek+、快仓、飞步科技、地平线生态合作伙伴、三一重工、柳工等
-人形 / 具身智能： 优必选、宇树 、智元、傅利叶等；</t>
-  </si>
-  <si>
-    <t>游戏 &amp; 图形渲染</t>
-  </si>
-  <si>
-    <t>中（客户端）
-高（引擎）</t>
-  </si>
-  <si>
-    <t>C++游戏客户端 / 游戏引擎 / 图形渲染 / 3D图形 / 图形中间件 / 游戏服务器 / 三维可视化 / 数字孪生可视化开发工程师</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.bilibili.com/video/BV1zMiQBvErD
-</t>
-  </si>
-  <si>
-    <t>腾讯游戏：王者荣耀、英雄联盟国服、DNF、天涯明月刀等网易互娱：梦幻西游、阴阳师、永劫无间
-米哈游：原神、崩坏、绝区零（大量 C++ + UE / 自研引擎）
-完美世界、西山居、游族、心动、鹰角等
-工业侧也有：华为、浪潮、广联达、三维家、CAXA、ZWSOFT（中望）做 3D 可视化、数字孪生</t>
   </si>
   <si>
     <t>其他</t>
@@ -420,6 +373,25 @@
 车路协同：RSU 侧边缘节点、V2X 协议栈、多源数据融合</t>
   </si>
   <si>
+    <t>机器人 / 智能制造 / 移动机器人（C++）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中偏高
+</t>
+  </si>
+  <si>
+    <t>工业机器人控制 / 机器人运动控制算法 / 移动机器人导航与路径规划 / 机器人上位机 / 机器人中间件/ 机器人仿真</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bilibili.com/video/BV1ApqfBAE9n
+</t>
+  </si>
+  <si>
+    <t>工业机器人：汇川、埃斯顿、新松、节卡 JAKA、遨博、ABB、KUKA、FANUC、安川等
+移动机器人：海柔创新、极智嘉 Geek+、快仓、飞步科技、地平线生态合作伙伴、三一重工、柳工等
+人形 / 具身智能： 优必选、宇树 、智元、傅利叶等；</t>
+  </si>
+  <si>
     <t>机器人学基础：坐标变换、DH 建模、正逆运动学、雅可比矩阵、轨迹规划、简单控制
 机器人中间件：ROS / ROS2，部分公司有自研 RT 框架；
 实时与通信：CAN/CANopen、EtherCAT、串口、UDP/TCP，自定义协议栈；
@@ -448,6 +420,21 @@
 SCADA/MES：数据采集、实时数据库、报警、报表、设备管理</t>
   </si>
   <si>
+    <t>嵌入式设备/消费电子 / IoT</t>
+  </si>
+  <si>
+    <t>低偏中
+（双非本）</t>
+  </si>
+  <si>
+    <t>嵌入式软件/ Linux软件 / MCU软件 / 单片机 / 物联网终端 / IoT网关 / 机顶盒软件 / 多媒体终端软件开发工程师</t>
+  </si>
+  <si>
+    <t>IoT 平台：涂鸦、机智云、阿里云 IoT、华为 HiLink 等
+智能硬件：小米生态链、绿米、各类做路由器、摄像头、穿戴公司
+家电：美的、格力、海尔等的智能家电控制板软件团队</t>
+  </si>
+  <si>
     <t>C/C++ + RTOS / 嵌入式 Linux
 板级驱动上层、设备应用程序、通信协议（MQTT、CoAP、自定义 TCP/UDP 协议）
 简单 UI（LVGL、Qt/Embedded）、低功耗优化、多任务调度</t>
@@ -456,6 +443,26 @@
     <t>C++ + Qt/MFC + 图像处理（OpenCV/VTK/ITK）
 医学图像：DICOM、PACS 系统，三维重建、切片浏览
 设备端：信号采集、图像重建、控制逻辑、病人监护</t>
+  </si>
+  <si>
+    <t>游戏 &amp; 图形渲染</t>
+  </si>
+  <si>
+    <t>中（客户端）
+高（引擎）</t>
+  </si>
+  <si>
+    <t>C++游戏客户端 / 游戏引擎 / 图形渲染 / 3D图形 / 图形中间件 / 游戏服务器 / 三维可视化 / 数字孪生可视化开发工程师</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bilibili.com/video/BV1zMiQBvErD
+</t>
+  </si>
+  <si>
+    <t>腾讯游戏：王者荣耀、英雄联盟国服、DNF、天涯明月刀等网易互娱：梦幻西游、阴阳师、永劫无间
+米哈游：原神、崩坏、绝区零（大量 C++ + UE / 自研引擎）
+完美世界、西山居、游族、心动、鹰角等
+工业侧也有：华为、浪潮、广联达、三维家、CAXA、ZWSOFT（中望）做 3D 可视化、数字孪生</t>
   </si>
   <si>
     <t>C++游戏引擎（Unreal 引擎 UE4/UE5、自研引擎）
@@ -1696,7 +1703,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1868,25 +1875,16 @@
     <xf numFmtId="49" fontId="31" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2745,7 +2743,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="中色系标题行标题列镶边行表格样式_29c806" count="11" xr9:uid="{D0A955CC-0745-49E6-8327-A7DEEEB3FB87}">
+    <tableStyle name="中色系标题行标题列镶边行表格样式_29c806" count="11" xr9:uid="{4548BE68-783B-43A6-B226-D21E32680E25}">
       <tableStyleElement type="wholeTable" dxfId="17"/>
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
@@ -2758,7 +2756,7 @@
       <tableStyleElement type="firstTotalCell" dxfId="8"/>
       <tableStyleElement type="lastTotalCell" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="中色系标题行标题列表格样式_008c58" count="12" xr9:uid="{9AD02FA5-92A2-426D-8132-1360B362AD90}">
+    <tableStyle name="中色系标题行标题列表格样式_008c58" count="12" xr9:uid="{E081A882-F5BE-4579-91FB-AB74E13A852C}">
       <tableStyleElement type="wholeTable" dxfId="29"/>
       <tableStyleElement type="headerRow" dxfId="28"/>
       <tableStyleElement type="totalRow" dxfId="27"/>
@@ -3043,7 +3041,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="38.9181818181818" customWidth="1"/>
@@ -3109,210 +3107,147 @@
       <c r="G3" s="49"/>
     </row>
     <row r="4" ht="105" customHeight="1" spans="1:7">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="E4" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="F4" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="G4" s="49"/>
+    </row>
+    <row r="5" ht="121.5" customHeight="1" spans="1:7">
+      <c r="A5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="49"/>
-    </row>
-    <row r="5" ht="105" customHeight="1" spans="1:7">
-      <c r="A5" s="50" t="s">
+      <c r="B5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="C5" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="53" t="s">
+      <c r="E5" s="52" t="s">
         <v>22</v>
       </c>
+      <c r="F5" s="56" t="s">
+        <v>23</v>
+      </c>
       <c r="G5" s="49"/>
     </row>
-    <row r="6" ht="121.5" customHeight="1" spans="1:7">
-      <c r="A6" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="54" t="s">
+    <row r="6" ht="154.5" customHeight="1" spans="1:7">
+      <c r="A6" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="B6" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="51" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="53" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="49"/>
     </row>
-    <row r="7" ht="154.5" customHeight="1" spans="1:7">
-      <c r="A7" s="50" t="s">
+    <row r="7" ht="121.5" customHeight="1" spans="1:7">
+      <c r="A7" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="E7" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="G7" s="49"/>
+    </row>
+    <row r="8" ht="138" customHeight="1" spans="1:7">
+      <c r="A8" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="B8" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="49"/>
-    </row>
-    <row r="8" ht="121.5" customHeight="1" spans="1:7">
-      <c r="A8" s="54" t="s">
+      <c r="C8" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="55" t="s">
+      <c r="E8" s="58" t="s">
         <v>35</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>32</v>
       </c>
       <c r="F8" s="56" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" ht="138" customHeight="1" spans="1:7">
+    <row r="9" ht="22.5" customHeight="1" spans="1:7">
       <c r="A9" s="54" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="56" t="s">
-        <v>40</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F9" s="60"/>
       <c r="G9" s="49"/>
     </row>
-    <row r="10" ht="121.5" customHeight="1" spans="1:7">
-      <c r="A10" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="50" t="s">
+    <row r="10" ht="39" customHeight="1" spans="1:7">
+      <c r="A10" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="B10" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="D10" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="53" t="s">
-        <v>45</v>
-      </c>
+      <c r="E10" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="60"/>
       <c r="G10" s="49"/>
-    </row>
-    <row r="11" ht="154.5" customHeight="1" spans="1:7">
-      <c r="A11" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="49"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A12" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="62"/>
-      <c r="G12" s="49"/>
-    </row>
-    <row r="13" ht="39" customHeight="1" spans="1:7">
-      <c r="A13" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="63" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="62"/>
-      <c r="G13" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3320,13 +3255,11 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="https://www.bilibili.com/video/BV1X12DB2EF2"/>
-    <hyperlink ref="E6" r:id="rId2" display="https://www.bilibili.com/video/BV1WJSvBcEQz&#10;本质还是linux后台技术栈（重点是网络）"/>
-    <hyperlink ref="E8" r:id="rId3" display="https://www.bilibili.com/video/BV1qzSjBeEFA" tooltip="https://www.bilibili.com/video/BV1qzSjBeEFA"/>
-    <hyperlink ref="E7" r:id="rId3" display="https://www.bilibili.com/video/BV1qzSjBeEFA"/>
-    <hyperlink ref="E10" r:id="rId4" display="https://www.bilibili.com/video/BV1ApqfBAE9n&#10;"/>
-    <hyperlink ref="E9" r:id="rId5" display="https://www.bilibili.com/video/BV1qbBKB3Euw&#10;"/>
-    <hyperlink ref="E11" r:id="rId6" display="https://www.bilibili.com/video/BV1zMiQBvErD&#10;"/>
-    <hyperlink ref="E13" r:id="rId5" display="https://www.bilibili.com/video/BV1qbBKB3Euw&#10;"/>
+    <hyperlink ref="E5" r:id="rId2" display="https://www.bilibili.com/video/BV1WJSvBcEQz&#10;本质还是linux后台技术栈（重点是网络）"/>
+    <hyperlink ref="E7" r:id="rId3" display="https://www.bilibili.com/video/BV1qzSjBeEFA" tooltip="https://www.bilibili.com/video/BV1qzSjBeEFA"/>
+    <hyperlink ref="E6" r:id="rId3" display="https://www.bilibili.com/video/BV1qzSjBeEFA"/>
+    <hyperlink ref="E8" r:id="rId4" display="https://www.bilibili.com/video/BV1qbBKB3Euw&#10;"/>
+    <hyperlink ref="E10" r:id="rId4" display="https://www.bilibili.com/video/BV1qbBKB3Euw&#10;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3381,177 +3314,177 @@
         <v>6</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="91" customHeight="1" spans="1:8">
       <c r="A3" s="26" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="H3" s="31"/>
     </row>
     <row r="4" ht="87.5" spans="1:8">
       <c r="A4" s="32" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="H4" s="31"/>
     </row>
     <row r="5" ht="95" customHeight="1" spans="1:8">
       <c r="A5" s="26" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H5" s="31"/>
     </row>
     <row r="6" ht="87.5" spans="1:8">
       <c r="A6" s="32" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G6" s="36" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H6" s="31"/>
     </row>
     <row r="7" ht="87.5" spans="1:8">
       <c r="A7" s="32" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="H7" s="31"/>
     </row>
     <row r="8" ht="99" customHeight="1" spans="1:8">
       <c r="A8" s="26" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="H8" s="31"/>
     </row>
     <row r="9" ht="87.5" spans="1:8">
       <c r="A9" s="26" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>79</v>
-      </c>
       <c r="G9" s="30" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H9" s="31"/>
     </row>
@@ -3575,76 +3508,76 @@
         <v>12</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H10" s="31"/>
     </row>
     <row r="11" ht="87.5" spans="1:8">
       <c r="A11" s="32" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="D11" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="41" t="s">
-        <v>17</v>
-      </c>
       <c r="F11" s="36" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="G11" s="36" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H11" s="31"/>
     </row>
     <row r="12" ht="87.5" spans="1:8">
       <c r="A12" s="26" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E12" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>22</v>
-      </c>
       <c r="G12" s="30" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H12" s="31"/>
     </row>
     <row r="13" ht="122.5" spans="1:8">
       <c r="A13" s="32" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B13" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>84</v>
@@ -3677,22 +3610,22 @@
     </row>
     <row r="15" ht="87.5" spans="1:8">
       <c r="A15" s="32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E15" s="42" t="s">
         <v>92</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>93</v>
@@ -3701,19 +3634,19 @@
     </row>
     <row r="16" ht="35" spans="1:8">
       <c r="A16" s="32" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
@@ -3721,19 +3654,19 @@
     </row>
     <row r="17" ht="63" spans="1:7">
       <c r="A17" s="32" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F17" s="36"/>
       <c r="G17" s="36"/>
